--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92570698933</v>
+        <v>46157.93106031632</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93106031632</v>
+        <v>46157.93176986248</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93176986248</v>
+        <v>46157.93402095042</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93402095042</v>
+        <v>46157.93720191978</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93720191978</v>
+        <v>46158.28218193222</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28218193222</v>
+        <v>46158.29691213326</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29691213326</v>
+        <v>46158.29817286327</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29817286327</v>
+        <v>46158.33389281286</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33389281286</v>
+        <v>46158.36859080601</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36859080601</v>
+        <v>46158.3728972996</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
